--- a/research/retail-competitors-indonesia/Riset_Pesaing_Kawan_Lama.xlsx
+++ b/research/retail-competitors-indonesia/Riset_Pesaing_Kawan_Lama.xlsx
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">Total GMV 2025 (US$ miliar)</t>
   </si>
   <si>
-    <t xml:space="preserve">Jumlah pangsa yang tercakup</t>
+    <t xml:space="preserve">Jumlah pangsa (101% karena pembulatan di sumber)</t>
   </si>
   <si>
     <t xml:space="preserve">Sumber utama</t>
